--- a/data/trans_dic/P6902-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,35; 66,06</t>
+          <t>34,07; 66,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,16; 73,97</t>
+          <t>41,06; 73,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,88; 68,21</t>
+          <t>41,78; 69,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,3; 75,53</t>
+          <t>32,09; 75,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,81; 81,75</t>
+          <t>46,11; 85,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,87; 96,48</t>
+          <t>69,64; 96,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,83; 77,89</t>
+          <t>45,89; 77,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,66; 65,94</t>
+          <t>27,46; 64,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,99; 67,88</t>
+          <t>43,38; 67,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,02; 80,73</t>
+          <t>58,58; 80,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49,46; 68,23</t>
+          <t>48,22; 69,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,58; 66,37</t>
+          <t>35,48; 66,25</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,52; 55,55</t>
+          <t>30,57; 55,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,12; 62,93</t>
+          <t>34,94; 62,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,51; 38,51</t>
+          <t>17,83; 38,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,1; 64,99</t>
+          <t>28,17; 64,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,99; 76,61</t>
+          <t>42,11; 74,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,03; 64,63</t>
+          <t>28,52; 65,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,67; 74,44</t>
+          <t>46,71; 75,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,2; 70,0</t>
+          <t>42,62; 68,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,1; 58,04</t>
+          <t>38,47; 58,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,34; 58,88</t>
+          <t>36,88; 61,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 47,49</t>
+          <t>29,84; 49,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,45; 61,58</t>
+          <t>39,17; 61,03</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,13; 58,65</t>
+          <t>26,06; 58,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,6; 48,85</t>
+          <t>14,85; 49,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 40,3</t>
+          <t>4,2; 37,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,14; 61,68</t>
+          <t>34,16; 61,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 35,93</t>
+          <t>4,56; 39,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,96; 76,12</t>
+          <t>26,65; 72,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 58,7</t>
+          <t>7,44; 58,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,49; 73,15</t>
+          <t>49,27; 73,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,82; 46,37</t>
+          <t>21,54; 46,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,68; 54,55</t>
+          <t>23,92; 53,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,7; 38,69</t>
+          <t>10,63; 39,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,22; 63,35</t>
+          <t>46,61; 64,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,29; 58,85</t>
+          <t>32,96; 59,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,91; 68,91</t>
+          <t>38,21; 68,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,49; 90,88</t>
+          <t>59,6; 89,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,96; 93,28</t>
+          <t>55,46; 92,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,14; 75,29</t>
+          <t>35,81; 76,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,87; 78,77</t>
+          <t>43,05; 79,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,91; 80,37</t>
+          <t>45,58; 79,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,92; 79,63</t>
+          <t>15,42; 81,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,45; 59,76</t>
+          <t>37,73; 60,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,34; 68,36</t>
+          <t>45,26; 67,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,61; 81,82</t>
+          <t>58,97; 82,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,73; 80,22</t>
+          <t>26,29; 80,12</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,34; 53,18</t>
+          <t>13,8; 52,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,16</t>
+          <t>0,0; 26,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,45; 87,8</t>
+          <t>39,24; 87,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,06; 76,7</t>
+          <t>36,77; 77,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,01; 100,0</t>
+          <t>29,39; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,25; 91,1</t>
+          <t>30,38; 90,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>57,99; 91,81</t>
+          <t>58,36; 92,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,95; 60,73</t>
+          <t>22,89; 57,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,23; 54,98</t>
+          <t>15,41; 54,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51,21; 90,8</t>
+          <t>53,03; 90,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,22; 78,07</t>
+          <t>50,38; 78,5</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,91; 58,6</t>
+          <t>27,53; 59,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,99; 64,12</t>
+          <t>33,11; 64,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,1; 47,19</t>
+          <t>12,77; 50,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36,2; 67,83</t>
+          <t>35,29; 67,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,86; 93,01</t>
+          <t>44,1; 92,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,95; 74,02</t>
+          <t>26,03; 73,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,49; 82,03</t>
+          <t>14,46; 87,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,09; 66,13</t>
+          <t>36,41; 65,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,63; 64,48</t>
+          <t>36,58; 62,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,02; 62,51</t>
+          <t>36,96; 61,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,24; 50,29</t>
+          <t>16,67; 52,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,79; 61,93</t>
+          <t>40,95; 63,47</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,0; 59,54</t>
+          <t>36,14; 59,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46,63; 74,46</t>
+          <t>45,54; 72,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,22; 53,05</t>
+          <t>29,45; 53,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54,91; 77,89</t>
+          <t>55,14; 78,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,58; 63,48</t>
+          <t>33,19; 63,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,17; 72,56</t>
+          <t>42,45; 71,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,63; 78,99</t>
+          <t>51,66; 79,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>65,48; 82,54</t>
+          <t>66,12; 82,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,8; 55,71</t>
+          <t>39,48; 57,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,64; 67,73</t>
+          <t>48,32; 68,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41,34; 60,3</t>
+          <t>42,96; 60,24</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,62; 77,7</t>
+          <t>63,21; 77,81</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,22; 49,68</t>
+          <t>31,5; 50,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,18; 48,77</t>
+          <t>20,49; 47,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35,86; 68,26</t>
+          <t>35,47; 67,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66,37; 89,33</t>
+          <t>67,13; 89,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,62; 57,05</t>
+          <t>29,53; 57,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,72; 65,37</t>
+          <t>24,27; 62,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,89; 67,7</t>
+          <t>25,14; 68,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,06; 84,6</t>
+          <t>46,66; 84,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,8; 50,33</t>
+          <t>33,55; 49,23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25,82; 49,31</t>
+          <t>25,66; 49,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,82; 61,76</t>
+          <t>35,87; 62,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>63,44; 83,91</t>
+          <t>63,11; 83,69</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,71; 48,01</t>
+          <t>39,26; 48,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40,96; 52,55</t>
+          <t>41,42; 52,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37,8; 48,77</t>
+          <t>37,98; 49,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56,4; 67,04</t>
+          <t>56,08; 67,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,02; 58,75</t>
+          <t>44,37; 57,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,04; 64,04</t>
+          <t>49,92; 64,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,61; 67,05</t>
+          <t>53,8; 66,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42,3; 68,86</t>
+          <t>42,76; 68,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42,18; 49,68</t>
+          <t>42,3; 49,9</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46,69; 55,53</t>
+          <t>46,55; 55,41</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45,38; 54,22</t>
+          <t>45,73; 54,37</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51,16; 66,32</t>
+          <t>50,36; 65,77</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14289; 28302</t>
+          <t>14597; 28276</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15686; 28189</t>
+          <t>15646; 27929</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23363; 39957</t>
+          <t>24474; 40446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7775; 18178</t>
+          <t>7723; 18082</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12825; 23397</t>
+          <t>13197; 24416</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20159; 29085</t>
+          <t>20994; 29126</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19553; 31845</t>
+          <t>18763; 31596</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3885; 10388</t>
+          <t>4327; 10200</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31440; 48511</t>
+          <t>31002; 47995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39603; 55098</t>
+          <t>39982; 55146</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49195; 67867</t>
+          <t>47956; 68852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13772; 26431</t>
+          <t>14129; 26382</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22819; 40219</t>
+          <t>22128; 39871</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19873; 35611</t>
+          <t>19770; 35620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15320; 31880</t>
+          <t>14758; 31774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12542; 30075</t>
+          <t>13037; 29927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14707; 25042</t>
+          <t>13765; 24491</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10303; 22177</t>
+          <t>9787; 22309</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19927; 31782</t>
+          <t>19945; 32327</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19179; 31809</t>
+          <t>19370; 31293</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40035; 60995</t>
+          <t>40423; 61383</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34850; 53528</t>
+          <t>33524; 55603</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36632; 59593</t>
+          <t>37443; 61894</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36189; 56479</t>
+          <t>35923; 55979</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9202; 21475</t>
+          <t>9542; 21277</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3695; 12362</t>
+          <t>3757; 12459</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>938; 8566</t>
+          <t>893; 7867</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16896; 30530</t>
+          <t>16910; 30437</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>991; 7806</t>
+          <t>990; 8675</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4835; 13651</t>
+          <t>4780; 13089</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>922; 7338</t>
+          <t>930; 7319</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23188; 33597</t>
+          <t>22628; 33676</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12727; 27051</t>
+          <t>12565; 27085</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10673; 23587</t>
+          <t>10343; 23125</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3612; 13061</t>
+          <t>3588; 13177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43147; 60452</t>
+          <t>44481; 61485</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19415; 34322</t>
+          <t>19225; 34460</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17440; 31701</t>
+          <t>17577; 31299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18988; 29505</t>
+          <t>19348; 29002</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23387; 37640</t>
+          <t>22379; 37298</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7978; 17096</t>
+          <t>8132; 17267</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11775; 23265</t>
+          <t>12715; 23372</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13145; 24057</t>
+          <t>13644; 23909</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12837; 64224</t>
+          <t>12439; 65381</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29534; 48423</t>
+          <t>30570; 48805</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34253; 51638</t>
+          <t>34186; 51289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35322; 51055</t>
+          <t>36798; 51205</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31137; 97070</t>
+          <t>31810; 96953</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3062; 12208</t>
+          <t>3168; 12035</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5200</t>
+          <t>0; 4281</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4677; 13056</t>
+          <t>5834; 13036</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6759; 13619</t>
+          <t>6529; 13708</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2022; 6970</t>
+          <t>2048; 6970</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3411; 10624</t>
+          <t>3542; 10599</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4246; 5771</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6371; 10086</t>
+          <t>6412; 10148</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7468; 18172</t>
+          <t>6849; 17214</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4239; 15302</t>
+          <t>4288; 15074</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10571; 18741</t>
+          <t>10946; 18740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14723; 22440</t>
+          <t>14481; 22564</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10831; 24503</t>
+          <t>11509; 24931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14313; 27814</t>
+          <t>14364; 28141</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2940; 10587</t>
+          <t>2864; 11374</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11445; 21445</t>
+          <t>11156; 21408</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6323; 13109</t>
+          <t>6216; 13077</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3789; 11239</t>
+          <t>3953; 11189</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1076; 6093</t>
+          <t>1074; 6472</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11510; 19981</t>
+          <t>11000; 19640</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20479; 36044</t>
+          <t>20447; 35095</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21683; 36610</t>
+          <t>21647; 36094</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5147; 15018</t>
+          <t>4978; 15629</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24605; 38293</t>
+          <t>25320; 39245</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>32723; 52665</t>
+          <t>31963; 52249</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25383; 40530</t>
+          <t>24789; 39713</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22895; 41561</t>
+          <t>23069; 41776</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40180; 56998</t>
+          <t>40353; 57128</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14619; 27634</t>
+          <t>14447; 27828</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19559; 33654</t>
+          <t>19690; 33095</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29864; 43982</t>
+          <t>28763; 44057</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>46183; 58212</t>
+          <t>46631; 58524</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>51212; 73521</t>
+          <t>52107; 75327</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49036; 68281</t>
+          <t>48708; 68848</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55411; 80816</t>
+          <t>57577; 80740</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>91426; 111658</t>
+          <t>90837; 111820</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>34001; 54106</t>
+          <t>34307; 54875</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9557; 22003</t>
+          <t>9247; 21572</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14085; 26810</t>
+          <t>13931; 26630</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37667; 50700</t>
+          <t>38101; 50567</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13753; 28401</t>
+          <t>14700; 28677</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7581; 20050</t>
+          <t>7444; 19245</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4898; 14488</t>
+          <t>5380; 14603</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27389; 46282</t>
+          <t>25526; 45957</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53646; 79871</t>
+          <t>53239; 78130</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19570; 37372</t>
+          <t>19446; 37628</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21733; 37475</t>
+          <t>21765; 38119</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>70711; 93536</t>
+          <t>70350; 93283</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>182842; 226766</t>
+          <t>185412; 229307</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>133156; 170842</t>
+          <t>134651; 170371</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>132290; 170699</t>
+          <t>132941; 171739</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>191466; 227618</t>
+          <t>190398; 227815</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>99095; 129325</t>
+          <t>97668; 126680</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>108010; 138217</t>
+          <t>107731; 138490</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>115947; 145027</t>
+          <t>116377; 144767</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>149821; 243927</t>
+          <t>151457; 241655</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>292085; 343979</t>
+          <t>292908; 345489</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>252559; 300396</t>
+          <t>251828; 299706</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>256966; 307060</t>
+          <t>258995; 307871</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>354902; 460070</t>
+          <t>349388; 456275</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6902-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,07; 66,0</t>
+          <t>32,64; 65,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,06; 73,29</t>
+          <t>41,25; 74,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,78; 69,05</t>
+          <t>41,42; 69,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,09; 75,12</t>
+          <t>20,21; 59,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,11; 85,32</t>
+          <t>47,63; 85,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,64; 96,62</t>
+          <t>67,18; 96,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,89; 77,28</t>
+          <t>47,14; 77,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,46; 64,74</t>
+          <t>25,06; 60,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,38; 67,16</t>
+          <t>43,24; 67,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,58; 80,8</t>
+          <t>56,55; 80,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,22; 69,23</t>
+          <t>47,32; 67,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,48; 66,25</t>
+          <t>28,19; 56,52</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,57; 55,07</t>
+          <t>30,28; 54,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,94; 62,94</t>
+          <t>35,12; 62,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 38,38</t>
+          <t>17,67; 38,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,17; 64,66</t>
+          <t>28,57; 64,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,11; 74,92</t>
+          <t>42,52; 76,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,52; 65,01</t>
+          <t>28,47; 64,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,71; 75,71</t>
+          <t>47,05; 76,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,62; 68,86</t>
+          <t>42,54; 67,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,47; 58,41</t>
+          <t>38,61; 58,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,88; 61,17</t>
+          <t>36,76; 59,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,84; 49,32</t>
+          <t>30,67; 48,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,17; 61,03</t>
+          <t>39,33; 61,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,06; 58,11</t>
+          <t>25,11; 57,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 49,24</t>
+          <t>14,74; 49,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 37,01</t>
+          <t>4,24; 35,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,16; 61,5</t>
+          <t>33,47; 61,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 39,93</t>
+          <t>4,57; 39,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,65; 72,98</t>
+          <t>24,95; 76,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 58,54</t>
+          <t>7,3; 56,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,27; 73,33</t>
+          <t>50,81; 73,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,54; 46,43</t>
+          <t>20,55; 46,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,92; 53,48</t>
+          <t>24,87; 54,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,63; 39,04</t>
+          <t>10,51; 38,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,61; 64,43</t>
+          <t>45,48; 63,31</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,96; 59,08</t>
+          <t>33,02; 58,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,21; 68,04</t>
+          <t>38,06; 68,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,6; 89,33</t>
+          <t>59,77; 90,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,46; 92,43</t>
+          <t>64,36; 92,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 76,05</t>
+          <t>38,67; 78,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,05; 79,13</t>
+          <t>43,38; 79,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,58; 79,87</t>
+          <t>42,98; 79,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,42; 81,07</t>
+          <t>61,87; 85,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,73; 60,23</t>
+          <t>37,81; 60,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,26; 67,9</t>
+          <t>45,37; 68,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,97; 82,06</t>
+          <t>57,75; 81,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,29; 80,12</t>
+          <t>68,9; 87,45</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,8; 52,43</t>
+          <t>12,06; 48,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,48</t>
+          <t>0,0; 33,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,24; 87,66</t>
+          <t>33,91; 88,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,77; 77,2</t>
+          <t>35,58; 73,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,39; 100,0</t>
+          <t>29,1; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,38; 90,89</t>
+          <t>25,97; 90,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,36; 92,37</t>
+          <t>53,41; 89,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,89; 57,52</t>
+          <t>22,72; 58,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,41; 54,17</t>
+          <t>14,14; 51,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,03; 90,79</t>
+          <t>53,54; 91,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,38; 78,5</t>
+          <t>47,66; 74,7</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,53; 59,63</t>
+          <t>26,57; 57,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,11; 64,87</t>
+          <t>35,04; 64,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,77; 50,7</t>
+          <t>12,62; 50,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,29; 67,71</t>
+          <t>32,08; 63,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,1; 92,79</t>
+          <t>44,83; 93,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,03; 73,69</t>
+          <t>25,06; 73,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,46; 87,14</t>
+          <t>14,56; 87,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,41; 65,0</t>
+          <t>37,08; 65,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,58; 62,78</t>
+          <t>37,32; 63,4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36,96; 61,63</t>
+          <t>35,73; 61,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16,67; 52,34</t>
+          <t>17,09; 53,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,95; 63,47</t>
+          <t>40,0; 60,52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,14; 59,07</t>
+          <t>36,3; 58,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45,54; 72,96</t>
+          <t>45,92; 72,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,45; 53,33</t>
+          <t>29,62; 52,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55,14; 78,07</t>
+          <t>51,52; 74,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,19; 63,92</t>
+          <t>33,69; 62,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,45; 71,36</t>
+          <t>40,85; 70,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,66; 79,12</t>
+          <t>52,69; 79,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66,12; 82,98</t>
+          <t>65,06; 82,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39,48; 57,07</t>
+          <t>40,13; 56,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,32; 68,29</t>
+          <t>48,37; 68,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,96; 60,24</t>
+          <t>42,98; 60,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,21; 77,81</t>
+          <t>61,77; 76,48</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,5; 50,38</t>
+          <t>31,95; 51,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,49; 47,81</t>
+          <t>21,23; 48,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35,47; 67,81</t>
+          <t>35,51; 67,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67,13; 89,09</t>
+          <t>66,85; 89,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,53; 57,6</t>
+          <t>28,89; 56,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,27; 62,74</t>
+          <t>23,31; 63,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,14; 68,24</t>
+          <t>23,16; 66,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>46,66; 84,0</t>
+          <t>66,34; 86,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,55; 49,23</t>
+          <t>32,96; 49,08</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25,66; 49,65</t>
+          <t>27,04; 48,72</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35,87; 62,83</t>
+          <t>36,59; 62,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>63,11; 83,69</t>
+          <t>70,62; 85,04</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39,26; 48,55</t>
+          <t>38,46; 48,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41,42; 52,4</t>
+          <t>41,03; 52,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37,98; 49,07</t>
+          <t>38,13; 49,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56,08; 67,1</t>
+          <t>55,96; 66,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,37; 57,55</t>
+          <t>44,12; 57,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,92; 64,17</t>
+          <t>49,47; 63,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,8; 66,93</t>
+          <t>53,42; 66,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42,76; 68,22</t>
+          <t>62,92; 71,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42,3; 49,9</t>
+          <t>41,73; 49,52</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46,55; 55,41</t>
+          <t>47,09; 55,93</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45,73; 54,37</t>
+          <t>45,54; 54,18</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50,36; 65,77</t>
+          <t>60,51; 67,9</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>17320</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14597; 28276</t>
+          <t>13983; 27898</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15646; 27929</t>
+          <t>15720; 28579</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24474; 40446</t>
+          <t>24262; 40775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7723; 18082</t>
+          <t>5298; 15496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13197; 24416</t>
+          <t>13633; 24431</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20994; 29126</t>
+          <t>20251; 29007</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18763; 31596</t>
+          <t>19273; 31763</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4327; 10200</t>
+          <t>4062; 9857</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31002; 47995</t>
+          <t>30898; 48380</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39982; 55146</t>
+          <t>38599; 54842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47956; 68852</t>
+          <t>47062; 67543</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14129; 26382</t>
+          <t>11956; 23973</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>21961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46105</t>
+          <t>47595</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22128; 39871</t>
+          <t>21921; 39705</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19770; 35620</t>
+          <t>19874; 35259</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14758; 31774</t>
+          <t>14624; 31709</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13037; 29927</t>
+          <t>13718; 30946</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13765; 24491</t>
+          <t>13899; 25007</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9787; 22309</t>
+          <t>9768; 22111</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19945; 32327</t>
+          <t>20088; 32461</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19370; 31293</t>
+          <t>19782; 31213</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40423; 61383</t>
+          <t>40572; 61473</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33524; 55603</t>
+          <t>33420; 53897</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37443; 61894</t>
+          <t>38484; 60278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35923; 55979</t>
+          <t>37175; 58529</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24003</t>
+          <t>23494</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28749</t>
+          <t>29556</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>53050</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9542; 21277</t>
+          <t>9193; 21170</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3757; 12459</t>
+          <t>3731; 12496</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>893; 7867</t>
+          <t>901; 7453</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16910; 30437</t>
+          <t>16602; 30252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>990; 8675</t>
+          <t>992; 8638</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4780; 13089</t>
+          <t>4474; 13670</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>930; 7319</t>
+          <t>913; 7056</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22628; 33676</t>
+          <t>23862; 34386</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12565; 27085</t>
+          <t>11991; 27172</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10343; 23125</t>
+          <t>10753; 23423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3588; 13177</t>
+          <t>3548; 12986</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44481; 61485</t>
+          <t>43915; 61128</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>44510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36183</t>
+          <t>40148</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67536</t>
+          <t>84659</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19225; 34460</t>
+          <t>19256; 34265</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17577; 31299</t>
+          <t>17508; 31526</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19348; 29002</t>
+          <t>19404; 29517</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22379; 37298</t>
+          <t>34862; 50364</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8132; 17267</t>
+          <t>8781; 17732</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12715; 23372</t>
+          <t>12811; 23337</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13644; 23909</t>
+          <t>12867; 23823</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12439; 65381</t>
+          <t>32966; 45428</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30570; 48805</t>
+          <t>30635; 49209</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34186; 51289</t>
+          <t>34270; 51504</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36798; 51205</t>
+          <t>36035; 50657</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31810; 96953</t>
+          <t>74039; 93969</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>22075</t>
         </is>
       </c>
     </row>
@@ -3041,32 +3041,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3168; 12035</t>
+          <t>2768; 11177</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4281</t>
+          <t>0; 5494</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5834; 13036</t>
+          <t>5043; 13107</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6529; 13708</t>
+          <t>7705; 15964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2048; 6970</t>
+          <t>2028; 6970</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3542; 10599</t>
+          <t>3029; 10589</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6412; 10148</t>
+          <t>7258; 12140</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6849; 17214</t>
+          <t>6798; 17633</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4288; 15074</t>
+          <t>3935; 14329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10946; 18740</t>
+          <t>11052; 18799</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14481; 22564</t>
+          <t>16797; 26327</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>31556</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11509; 24931</t>
+          <t>11110; 24091</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14364; 28141</t>
+          <t>15202; 27963</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2864; 11374</t>
+          <t>2832; 11270</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11156; 21408</t>
+          <t>10543; 20997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6216; 13077</t>
+          <t>6318; 13212</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3953; 11189</t>
+          <t>3805; 11210</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1074; 6472</t>
+          <t>1081; 6493</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11000; 19640</t>
+          <t>11339; 20121</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20447; 35095</t>
+          <t>20865; 35441</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21647; 36094</t>
+          <t>20923; 36142</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4978; 15629</t>
+          <t>5103; 15910</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25320; 39245</t>
+          <t>25378; 38400</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49341</t>
+          <t>55449</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>102256</t>
+          <t>115459</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31963; 52249</t>
+          <t>32111; 51309</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24789; 39713</t>
+          <t>24997; 39531</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23069; 41776</t>
+          <t>23208; 41271</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40353; 57128</t>
+          <t>44230; 64361</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14447; 27828</t>
+          <t>14668; 27374</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19690; 33095</t>
+          <t>18948; 32469</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28763; 44057</t>
+          <t>29338; 44015</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>46631; 58524</t>
+          <t>52516; 66458</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52107; 75327</t>
+          <t>52971; 74801</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48708; 68848</t>
+          <t>48761; 69029</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57577; 80740</t>
+          <t>57602; 80808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>90837; 111820</t>
+          <t>102889; 127389</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44979</t>
+          <t>53312</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>39701</t>
+          <t>44920</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84679</t>
+          <t>98233</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>34307; 54875</t>
+          <t>34797; 55872</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9247; 21572</t>
+          <t>9577; 21886</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13931; 26630</t>
+          <t>13945; 26458</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38101; 50567</t>
+          <t>44558; 59586</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14700; 28677</t>
+          <t>14382; 27927</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7444; 19245</t>
+          <t>7149; 19367</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5380; 14603</t>
+          <t>4957; 14203</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25526; 45957</t>
+          <t>38135; 49695</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53239; 78130</t>
+          <t>52310; 77886</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19446; 37628</t>
+          <t>20491; 36924</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21765; 38119</t>
+          <t>22200; 37761</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>70350; 93283</t>
+          <t>87667; 105563</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>209966</t>
+          <t>237215</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>214322</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>424288</t>
+          <t>469947</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>185412; 229307</t>
+          <t>181641; 228714</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>134651; 170371</t>
+          <t>133393; 169246</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>132941; 171739</t>
+          <t>133469; 171833</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>190398; 227815</t>
+          <t>215437; 255905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>97668; 126680</t>
+          <t>97113; 126572</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>107731; 138490</t>
+          <t>106769; 137870</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>116377; 144767</t>
+          <t>115538; 144165</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>151457; 241655</t>
+          <t>217276; 247807</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>292908; 345489</t>
+          <t>288922; 342872</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>251828; 299706</t>
+          <t>254735; 302557</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>258995; 307871</t>
+          <t>257887; 306843</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>349388; 456275</t>
+          <t>441934; 495872</t>
         </is>
       </c>
     </row>
